--- a/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
+++ b/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Equity" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Debt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$G$1238</definedName>
@@ -153,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -190,6 +191,9 @@
     <xf numFmtId="4" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4638,7 +4642,7 @@
         <v>1205.65</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>1172.87</v>
+        <v>1172.86</v>
       </c>
       <c r="F156" s="4">
         <f>C156/C155-1</f>
@@ -7288,7 +7292,7 @@
         <v>1384.88</v>
       </c>
       <c r="E262" s="3" t="n">
-        <v>1353.02</v>
+        <v>1353.01</v>
       </c>
       <c r="F262" s="4">
         <f>C262/C261-1</f>
@@ -22088,7 +22092,7 @@
         <v>1384.35</v>
       </c>
       <c r="E854" s="3" t="n">
-        <v>1365.08</v>
+        <v>1365.09</v>
       </c>
       <c r="F854" s="4">
         <f>C854/C853-1</f>
@@ -31679,16 +31683,16 @@
         <v>46276</v>
       </c>
       <c r="B1238" s="3" t="n">
-        <v>23292.35</v>
+        <v>23302.45</v>
       </c>
       <c r="C1238" s="3" t="n">
-        <v>23292.35</v>
+        <v>23302.45</v>
       </c>
       <c r="D1238" s="3" t="n">
-        <v>1554.9</v>
+        <v>1555.9</v>
       </c>
       <c r="E1238" s="3" t="n">
-        <v>1554.9</v>
+        <v>1555.9</v>
       </c>
       <c r="F1238" s="4">
         <f>C1238/C1237-1</f>
@@ -33007,7 +33011,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="100" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Weighted Average Cost of Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>WACC  =  We x Ke  +  Wd x Kd x (1 - tax rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Blue = hardcoded input (sourced on Notes)   Green = linked from another sheet   Black = formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1. Market value of equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Shares outstanding</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>1017766288</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Ordinary shares at 31-Mar-2026. Reconciles to the Rs 102 crore equity capital at Re 1 face value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Share price (INR)</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>Data!D1238</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Latest unadjusted close on the Data sheet. Unadjusted is correct here - market cap needs the traded price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Market value of equity (INR crore)</t>
+        </is>
+      </c>
+      <c r="B8" s="30">
+        <f>B6*B7/10000000</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Shares x price, converted to crore (1 crore = 10,000,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2. Market value of debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Total borrowings (INR crore)</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>'Cost of Debt'!E7</f>
+        <v/>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>FY2026 closing borrowings, linked from the Cost of Debt sheet. Book value is the standard proxy for the market value of debt: the borrowings are short-dated and floating, so book and market value are close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>3. Capital structure weights</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Total capital (D + E)</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>B8+B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Weight of equity (We)</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>B8/B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Weight of debt (Wd)</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>B11/B14</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Under 1%. Pidilite is financed almost entirely by equity, so WACC lands within a few basis points of Ke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>4. Component costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B19" s="33">
+        <f>'Cost of Equity'!B29</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Linked from the Cost of Equity sheet - CAPM on the regression beta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Cost of debt, pre-tax (Kd)</t>
+        </is>
+      </c>
+      <c r="B20" s="33">
+        <f>'Cost of Debt'!E12</f>
+        <v/>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>FY2026 total interest / total borrowings, linked from the Cost of Debt sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>'Cost of Debt'!E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Cost of debt, after tax</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B20*(1-B21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Interest is tax-deductible, so only the after-tax cost is borne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>5. WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Equity contribution</t>
+        </is>
+      </c>
+      <c r="B25" s="16">
+        <f>B15*B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Debt contribution</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>B16*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B27" s="23">
+        <f>B25+B26</f>
+        <v/>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>We x Ke + Wd x after-tax Kd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>WACC less Ke</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>B27-B19</f>
+        <v/>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>A few basis points. With a sub-1% debt weight the capital structure barely moves the number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>6. Memo - net cash position</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>232.49</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>31-Mar-2026 consolidated balance sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Cash + short-term investments</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>4215.98</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Includes liquid investments held as treasury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Net debt (borrowings - cash &amp; investments)</t>
+        </is>
+      </c>
+      <c r="B33" s="30">
+        <f>B11-B32</f>
+        <v/>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>NEGATIVE - Pidilite holds far more cash and liquid investments than borrowings, so it is net cash. A net-debt-weighted WACC is not meaningful here; the gross-debt weighting above is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>7. Sensitivity - WACC at a target debt weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Actual gearing is under 1%, so this shows what WACC would be if Pidilite levered up, holding Ke and after-tax Kd at their current values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Ke \ Wd</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D37" s="34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E37" s="34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B38" s="26">
+        <f>(1-B$37)*$A38+B$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="C38" s="26">
+        <f>(1-C$37)*$A38+C$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>(1-D$37)*$A38+D$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="E38" s="26">
+        <f>(1-E$37)*$A38+E$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="F38" s="26">
+        <f>(1-F$37)*$A38+F$37*$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B39" s="26">
+        <f>(1-B$37)*$A39+B$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="C39" s="26">
+        <f>(1-C$37)*$A39+C$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="D39" s="26">
+        <f>(1-D$37)*$A39+D$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="E39" s="26">
+        <f>(1-E$37)*$A39+E$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="F39" s="26">
+        <f>(1-F$37)*$A39+F$37*$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B40" s="26">
+        <f>(1-B$37)*$A40+B$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="C40" s="26">
+        <f>(1-C$37)*$A40+C$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>(1-D$37)*$A40+D$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="E40" s="26">
+        <f>(1-E$37)*$A40+E$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="F40" s="26">
+        <f>(1-F$37)*$A40+F$37*$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B41" s="26">
+        <f>(1-B$37)*$A41+B$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="C41" s="26">
+        <f>(1-C$37)*$A41+C$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>(1-D$37)*$A41+D$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="E41" s="26">
+        <f>(1-E$37)*$A41+E$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="F41" s="26">
+        <f>(1-F$37)*$A41+F$37*$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="B42" s="26">
+        <f>(1-B$37)*$A42+B$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="C42" s="26">
+        <f>(1-C$37)*$A42+C$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="D42" s="26">
+        <f>(1-D$37)*$A42+D$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="E42" s="26">
+        <f>(1-E$37)*$A42+E$37*$B$22</f>
+        <v/>
+      </c>
+      <c r="F42" s="26">
+        <f>(1-F$37)*$A42+F$37*$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Each cell = (1 - Wd) x Ke + Wd x after-tax Kd, using the after-tax Kd in B22.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -33034,7 +33553,7 @@
           <t>NIFTY 50 (x axis)</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Yahoo Finance symbol ^NSEI — NSE India benchmark index.</t>
         </is>
@@ -33046,7 +33565,7 @@
           <t>Pidilite (y axis)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Yahoo Finance symbol PIDILITIND.NS — Pidilite Industries Ltd, NSE India. Interpreted as the requested 'Pidilite Inc'; there is no separately listed entity by that exact name.</t>
         </is>
@@ -33065,7 +33584,7 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Yahoo Finance chart API (query1.finance.yahoo.com/v8/finance/chart), range=5y, interval=1d, retrieved 2026-09-05.</t>
         </is>
@@ -33077,7 +33596,7 @@
           <t>Period covered</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>2021-09-13 to 2026-09-11 (5 years of daily bars).</t>
         </is>
@@ -33089,7 +33608,7 @@
           <t>Rows on Data sheet</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>1237 trading days common to both series; 1236 daily returns (the first date has no prior close).</t>
         </is>
@@ -33101,7 +33620,7 @@
           <t>Alignment</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Dates are inner-joined, so only sessions on which both the index and the stock traded are kept. This avoids spurious zero or stale returns on non-common holidays.</t>
         </is>
@@ -33113,7 +33632,7 @@
           <t>Prices</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Both raw Close and Adjusted Close are shown. Adjusted Close is corrected for splits and dividends.</t>
         </is>
@@ -33132,7 +33651,7 @@
           <t>Daily % return</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>(Adjusted Close today / Adjusted Close previous session) - 1, computed on Adjusted Close so the series is a total return. Stored as a fraction and displayed as a percentage.</t>
         </is>
@@ -33144,7 +33663,7 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Ordinary least squares SLOPE(y, x) with NIFTY 50 returns as x and Pidilite returns as y. This is Pidilite's raw (unadjusted) beta against the NIFTY 50.</t>
         </is>
@@ -33156,7 +33675,7 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Slope is unit-free: it is identical whether both series are expressed as fractions or as percentages.</t>
         </is>
@@ -33168,7 +33687,7 @@
           <t>Annualisation</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Daily volatility x SQRT(252). 252 trading days per year is an assumption, set in cell Regression!B21.</t>
         </is>
@@ -33187,7 +33706,7 @@
           <t>Independent check</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>The workbook's cells hold live formulas, not pasted numbers, and Excel recalculates them on open. The same regression computed independently in Python (numpy least squares) at build time gave: n = 1236  |  slope (beta) = 0.6903  |  intercept = 0.0134% per day  |  R-squared = 0.1973  |  correlation = 0.4442. The Regression sheet's 'Slope cross-check (Cov / Var)' cell is a second, in-sheet check that must match the SLOPE result.</t>
         </is>
@@ -33199,7 +33718,7 @@
           <t>Recalculation</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>This file was written by openpyxl, which stores formulas without cached results. Full-calculation-on-load is set, so Excel or LibreOffice fills in every value the first time the file is opened.</t>
         </is>
@@ -33218,7 +33737,7 @@
           <t>Risk-free rate</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>6.97% - India 10-year benchmark G-Sec yield as at 10-Sep-2026, Trading Economics (https://tradingeconomics.com/india/government-bond-yield). Cross-checked at 6.96% on 04-Sep-2026. A 10Y sovereign yield is the conventional Rf for an INR-denominated valuation.</t>
         </is>
@@ -33230,7 +33749,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Linked live to Regression!B4 - the OLS slope computed on this workbook's own daily returns. Not retyped.</t>
         </is>
@@ -33242,7 +33761,7 @@
           <t>Market return</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>^NSEI is a PRICE index and excludes dividends, so a dividend yield of 1.25% (NIFTY 50 long-run average) is added to every price CAGR to reach a total market return.</t>
         </is>
@@ -33254,7 +33773,7 @@
           <t>Why three approaches</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>The trailing 5-year window opens close to the Sep-2021 market peak, so the realised NIFTY 50 total return lands within a few tenths of a percent of the risk-free rate. The resulting risk premium is approximately zero - and on a marginally different start date it goes negative, putting the cost of equity below Rf. Either way it is an artefact of the start date, not an economic result, and cannot be used on its own. Approaches B (10-year realised) and C (forward-looking implied premium) are shown alongside it, and the selected-Ke cell defaults to C.</t>
         </is>
@@ -33266,7 +33785,7 @@
           <t>India ERP</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>7.08% - Damodaran implied India equity risk premium, January 2026 vintage (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), being the mature-market ERP plus a 2.85% India country risk premium at a Baa3 rating. A July-2026 update quotes 7.31%.</t>
         </is>
@@ -33278,7 +33797,7 @@
           <t>10-year CAGRs</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>NIFTY 50 price CAGR 10.49% and Pidilite total-return CAGR 16.46%, both over the 10 years to 11-Sep-2026, computed from the full Yahoo Finance price history (a longer window than this workbook's 5-year Data sheet).</t>
         </is>
@@ -33297,7 +33816,7 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Pidilite Industries Ltd CONSOLIDATED annual financials, FY2023-FY2026 (years ended 31 March). Retrieved from the Yahoo Finance fundamentals-timeseries API and cross-checked line by line against screener.in (https://www.screener.in/company/PIDILITIND/consolidated/). Both restate the same statements the company files with the exchanges; every figure used agreed between the two sources.</t>
         </is>
@@ -33309,7 +33828,7 @@
           <t>NSE not reachable</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>www.nseindia.com returns HTTP 403 to this environment (NSE blocks datacentre traffic), so the figures could not be pulled from NSE directly. The two sources above carry the same filed consolidated numbers.</t>
         </is>
@@ -33321,7 +33840,7 @@
           <t>Borrowings definition</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>The 'Total borrowings' line is the borrowings figure as reported, which under Ind AS 116 INCLUDES lease liabilities - and finance costs likewise include lease interest, so numerator and denominator are consistent. Pidilite is close to debt-free: of FY2026 borrowings of Rs 417.21 crore, only Rs 105.91 crore is actual borrowing and the rest is lease liability. Dividing total interest by borrowings-excluding-leases would mismatch the two, and is shown on the sheet only as a memo.</t>
         </is>
@@ -33333,38 +33852,93 @@
           <t>Closing vs average</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>The headline follows the requested formula (total interest / total borrowings) on closing balances. A cost of debt on AVERAGE borrowings is shown alongside, since interest accrues across the year.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Market value of equity = 1,017,766,288 shares outstanding at 31-Mar-2026 x the latest unadjusted close from the Data sheet. Market value of debt is taken at book: the borrowings are short-dated and largely floating or lease obligations, so book value is a close proxy and is the normal convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Shares outstanding</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>1,017,766,288 ordinary shares at 31-Mar-2026 (Yahoo Finance fundamentals; reconciles to the Rs 102 crore equity capital reported by screener.in at Re 1 face value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>Near-zero gearing</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>Debt is under 1% of total capital, so WACC sits within a few basis points of the cost of equity. The sensitivity grid on the WACC sheet shows what the number would become at higher target debt weights, holding the component costs fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Net cash</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Cash and equivalents of Rs 232.49 crore and cash plus short-term investments of Rs 4,215.98 crore at 31-Mar-2026 both exceed total borrowings of Rs 417.21 crore, so Pidilite is net cash. Net debt is negative, which makes a net-debt-weighted WACC meaningless; gross debt is used for the weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Raw beta</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>No Blume or Vasicek adjustment and no risk-free rate is subtracted; this is a total-return beta, not a CAPM excess-return beta.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>Beta estimated over a 5-year window is a single point estimate and is not stable over sub-periods.</t>
         </is>

--- a/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
+++ b/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Equity" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Debt" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$G$1238</definedName>
@@ -23,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.00%;(0.00%);-"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="0.00000000"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -154,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -194,6 +196,12 @@
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4642,7 +4650,7 @@
         <v>1205.65</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>1172.86</v>
+        <v>1172.87</v>
       </c>
       <c r="F156" s="4">
         <f>C156/C155-1</f>
@@ -7292,7 +7300,7 @@
         <v>1384.88</v>
       </c>
       <c r="E262" s="3" t="n">
-        <v>1353.01</v>
+        <v>1353.02</v>
       </c>
       <c r="F262" s="4">
         <f>C262/C261-1</f>
@@ -22092,7 +22100,7 @@
         <v>1384.35</v>
       </c>
       <c r="E854" s="3" t="n">
-        <v>1365.09</v>
+        <v>1365.08</v>
       </c>
       <c r="F854" s="4">
         <f>C854/C853-1</f>
@@ -31683,16 +31691,16 @@
         <v>46276</v>
       </c>
       <c r="B1238" s="3" t="n">
-        <v>23302.45</v>
+        <v>23289.55</v>
       </c>
       <c r="C1238" s="3" t="n">
-        <v>23302.45</v>
+        <v>23289.55</v>
       </c>
       <c r="D1238" s="3" t="n">
-        <v>1555.9</v>
+        <v>1555</v>
       </c>
       <c r="E1238" s="3" t="n">
-        <v>1555.9</v>
+        <v>1555</v>
       </c>
       <c r="F1238" s="4">
         <f>C1238/C1237-1</f>
@@ -33526,7 +33534,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="100" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cash Flow Projections and DCF Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>FCFF  =  EBIT x (1 - tax)  +  D&amp;A  -  Capex  -  Increase in net working capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Blue = hardcoded input   Green = linked from another sheet   Black = formula.  All figures INR crore unless stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1. Historical performance (reported actuals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>11751.62</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>12337.07</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>13092.76</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>14551.26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>EBIT (operating income)</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>1752.01</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>2402.73</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>2673.41</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>3147.99</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Operating income, which EXCLUDES other income - treasury income is captured separately via net cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EBIT margin</t>
+        </is>
+      </c>
+      <c r="B9" s="16">
+        <f>B8/B7</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>C8/C7</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>D8/D7</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>E8/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>269.74</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>350.45</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>388.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>B10/B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="16">
+        <f>C10/C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>D10/D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>E10/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>505.35</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>558.71</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>452.34</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>592.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>B12/B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>C12/C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>D12/D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>E12/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>1459.14</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>768.97</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>824.87</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>836.4400000000001</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Current assets less cash and investments, less current liabilities excluding current debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NWC % of revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>B14/B7</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>C14/C7</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>D14/D7</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>E14/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revenue growth</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>C7/B7-1</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>D7/C7-1</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>E7/D7-1</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>FY2024-FY2026 growth of 5.0%, 6.1% and 11.1%; three-year revenue CAGR 7.4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2. Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>EBIT margin (held flat)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>FY2026 actual. Margin rose from 14.9% to 21.6% over four years on softer input costs; holding it flat rather than extrapolating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Three-year average (FY2024-FY2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Four-year average. Above D&amp;A, consistent with a growing asset base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>NWC % of incremental revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Three-year average NWC intensity. Applied to the CHANGE in revenue, so no step change in the NWC level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="B23" s="33">
+        <f>'Cost of Debt'!E18</f>
+        <v/>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Linked from the Cost of Debt sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>WACC (discount rate)</t>
+        </is>
+      </c>
+      <c r="B24" s="33">
+        <f>WACC!B27</f>
+        <v/>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Linked from the WACC sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Perpetual nominal growth. Must stay below WACC, and below the 6.97% risk-free rate - no firm outgrows its economy forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>3. Free cash flow projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Fades from 10% toward the 5% terminal rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="30">
+        <f>E7*(1+B29)</f>
+        <v/>
+      </c>
+      <c r="C30" s="30">
+        <f>B30*(1+C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="30">
+        <f>C30*(1+D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="30">
+        <f>D30*(1+E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="30">
+        <f>E30*(1+F29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>FY2027 grows off the FY2026 actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B31" s="30">
+        <f>B30*$B$19</f>
+        <v/>
+      </c>
+      <c r="C31" s="30">
+        <f>C30*$B$19</f>
+        <v/>
+      </c>
+      <c r="D31" s="30">
+        <f>D30*$B$19</f>
+        <v/>
+      </c>
+      <c r="E31" s="30">
+        <f>E30*$B$19</f>
+        <v/>
+      </c>
+      <c r="F31" s="30">
+        <f>F30*$B$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Less: tax on EBIT</t>
+        </is>
+      </c>
+      <c r="B32" s="30">
+        <f>-B31*$B$23</f>
+        <v/>
+      </c>
+      <c r="C32" s="30">
+        <f>-C31*$B$23</f>
+        <v/>
+      </c>
+      <c r="D32" s="30">
+        <f>-D31*$B$23</f>
+        <v/>
+      </c>
+      <c r="E32" s="30">
+        <f>-E31*$B$23</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>-F31*$B$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B33" s="30">
+        <f>B31+B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="30">
+        <f>C31+C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="30">
+        <f>D31+D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="30">
+        <f>E31+E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>F31+F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Add: D&amp;A</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>B30*$B$20</f>
+        <v/>
+      </c>
+      <c r="C34" s="30">
+        <f>C30*$B$20</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>D30*$B$20</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>E30*$B$20</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>F30*$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Less: capex</t>
+        </is>
+      </c>
+      <c r="B35" s="30">
+        <f>-B30*$B$21</f>
+        <v/>
+      </c>
+      <c r="C35" s="30">
+        <f>-C30*$B$21</f>
+        <v/>
+      </c>
+      <c r="D35" s="30">
+        <f>-D30*$B$21</f>
+        <v/>
+      </c>
+      <c r="E35" s="30">
+        <f>-E30*$B$21</f>
+        <v/>
+      </c>
+      <c r="F35" s="30">
+        <f>-F30*$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Less: increase in NWC</t>
+        </is>
+      </c>
+      <c r="B36" s="30">
+        <f>-(B30-E7)*$B$22</f>
+        <v/>
+      </c>
+      <c r="C36" s="30">
+        <f>-(C30-B30)*$B$22</f>
+        <v/>
+      </c>
+      <c r="D36" s="30">
+        <f>-(D30-C30)*$B$22</f>
+        <v/>
+      </c>
+      <c r="E36" s="30">
+        <f>-(E30-D30)*$B$22</f>
+        <v/>
+      </c>
+      <c r="F36" s="30">
+        <f>-(F30-E30)*$B$22</f>
+        <v/>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>NWC intensity applied to the increase in revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>FREE CASH FLOW TO FIRM (FCFF)</t>
+        </is>
+      </c>
+      <c r="B37" s="35">
+        <f>B33+B34+B35+B36</f>
+        <v/>
+      </c>
+      <c r="C37" s="35">
+        <f>C33+C34+C35+C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="35">
+        <f>D33+D34+D35+D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="35">
+        <f>E33+E34+E35+E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="35">
+        <f>F33+F34+F35+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>End-of-period discounting from the 31-Mar-2026 balance sheet date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>1/(1+$B$24)^B38</f>
+        <v/>
+      </c>
+      <c r="C39" s="13">
+        <f>1/(1+$B$24)^C38</f>
+        <v/>
+      </c>
+      <c r="D39" s="13">
+        <f>1/(1+$B$24)^D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="13">
+        <f>1/(1+$B$24)^E38</f>
+        <v/>
+      </c>
+      <c r="F39" s="13">
+        <f>1/(1+$B$24)^F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>PV of FCFF</t>
+        </is>
+      </c>
+      <c r="B40" s="30">
+        <f>B37*B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="30">
+        <f>C37*C39</f>
+        <v/>
+      </c>
+      <c r="D40" s="30">
+        <f>D37*D39</f>
+        <v/>
+      </c>
+      <c r="E40" s="30">
+        <f>E37*E39</f>
+        <v/>
+      </c>
+      <c r="F40" s="30">
+        <f>F37*F39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>4. Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Sum of PV of forecast FCFF</t>
+        </is>
+      </c>
+      <c r="B43" s="30">
+        <f>SUM(B40:F40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value (Gordon growth)</t>
+        </is>
+      </c>
+      <c r="B44" s="30">
+        <f>F37*(1+$B$25)/($B$24-$B$25)</f>
+        <v/>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>FY2031 FCFF grown one year, capitalised at WACC less terminal growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B45" s="30">
+        <f>B44*F39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B46" s="30">
+        <f>B43+B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B47" s="16">
+        <f>B45/B46</f>
+        <v/>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Above ~75% means the answer rests mainly on the terminal assumptions rather than the forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Less: net debt</t>
+        </is>
+      </c>
+      <c r="B48" s="32">
+        <f>WACC!B33</f>
+        <v/>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Negative - Pidilite is net cash, so this ADDS to equity value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B49" s="30">
+        <f>B46-B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Shares outstanding (crore)</t>
+        </is>
+      </c>
+      <c r="B50" s="37">
+        <f>WACC!B6/10000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>INTRINSIC VALUE PER SHARE (INR)</t>
+        </is>
+      </c>
+      <c r="B51" s="38">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Current market price (INR)</t>
+        </is>
+      </c>
+      <c r="B52" s="32">
+        <f>WACC!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>B51/B52-1</f>
+        <v/>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Large negative: Pidilite trades on a premium multiple that this set of assumptions does not support. See section 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>5. Sensitivity - value per share vs WACC and terminal growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>WACC \ g</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D56" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E56" s="24" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F56" s="24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="B57" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A57)^$B$38:$F$38)+$F$37*(1+B$56)/($A57-B$56)/(1+$A57)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="C57" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A57)^$B$38:$F$38)+$F$37*(1+C$56)/($A57-C$56)/(1+$A57)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="D57" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A57)^$B$38:$F$38)+$F$37*(1+D$56)/($A57-D$56)/(1+$A57)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="E57" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A57)^$B$38:$F$38)+$F$37*(1+E$56)/($A57-E$56)/(1+$A57)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="F57" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A57)^$B$38:$F$38)+$F$37*(1+F$56)/($A57-F$56)/(1+$A57)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="B58" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A58)^$B$38:$F$38)+$F$37*(1+B$56)/($A58-B$56)/(1+$A58)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="C58" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A58)^$B$38:$F$38)+$F$37*(1+C$56)/($A58-C$56)/(1+$A58)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="D58" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A58)^$B$38:$F$38)+$F$37*(1+D$56)/($A58-D$56)/(1+$A58)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="E58" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A58)^$B$38:$F$38)+$F$37*(1+E$56)/($A58-E$56)/(1+$A58)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="F58" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A58)^$B$38:$F$38)+$F$37*(1+F$56)/($A58-F$56)/(1+$A58)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="B59" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A59)^$B$38:$F$38)+$F$37*(1+B$56)/($A59-B$56)/(1+$A59)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="C59" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A59)^$B$38:$F$38)+$F$37*(1+C$56)/($A59-C$56)/(1+$A59)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="D59" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A59)^$B$38:$F$38)+$F$37*(1+D$56)/($A59-D$56)/(1+$A59)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="E59" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A59)^$B$38:$F$38)+$F$37*(1+E$56)/($A59-E$56)/(1+$A59)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="F59" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A59)^$B$38:$F$38)+$F$37*(1+F$56)/($A59-F$56)/(1+$A59)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="B60" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A60)^$B$38:$F$38)+$F$37*(1+B$56)/($A60-B$56)/(1+$A60)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="C60" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A60)^$B$38:$F$38)+$F$37*(1+C$56)/($A60-C$56)/(1+$A60)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="D60" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A60)^$B$38:$F$38)+$F$37*(1+D$56)/($A60-D$56)/(1+$A60)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="E60" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A60)^$B$38:$F$38)+$F$37*(1+E$56)/($A60-E$56)/(1+$A60)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="F60" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A60)^$B$38:$F$38)+$F$37*(1+F$56)/($A60-F$56)/(1+$A60)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="B61" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A61)^$B$38:$F$38)+$F$37*(1+B$56)/($A61-B$56)/(1+$A61)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="C61" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A61)^$B$38:$F$38)+$F$37*(1+C$56)/($A61-C$56)/(1+$A61)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="D61" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A61)^$B$38:$F$38)+$F$37*(1+D$56)/($A61-D$56)/(1+$A61)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="E61" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A61)^$B$38:$F$38)+$F$37*(1+E$56)/($A61-E$56)/(1+$A61)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+      <c r="F61" s="40">
+        <f>(SUMPRODUCT($B$37:$F$37/(1+$A61)^$B$38:$F$38)+$F$37*(1+F$56)/($A61-F$56)/(1+$A61)^$F$38-$B$48)/$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Each cell re-runs the whole DCF at that WACC and terminal growth rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>6. Reverse DCF - what the market price implies</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Enterprise value at market price</t>
+        </is>
+      </c>
+      <c r="B65" s="32">
+        <f>WACC!B8+WACC!B33</f>
+        <v/>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Market capitalisation plus net debt (which is negative here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value the market implies</t>
+        </is>
+      </c>
+      <c r="B66" s="30">
+        <f>(B65-B43)/F39</f>
+        <v/>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Market EV less the PV of the forecast FCFF, un-discounted back to FY2031.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Implied perpetual growth rate</t>
+        </is>
+      </c>
+      <c r="B67" s="16">
+        <f>(B66*$B$24-F37)/(B66+F37)</f>
+        <v/>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Solving Gordon growth backwards. Compare with the 6.97% risk-free rate: a perpetual rate above it implies the company eventually outgrows the whole economy, so the market is pricing in either much stronger growth, higher margins, or a lower risk premium than this model assumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Read this section before treating the downside above as a recommendation - it shows which assumption the gap actually lives in.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -33553,7 +34709,7 @@
           <t>NIFTY 50 (x axis)</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Yahoo Finance symbol ^NSEI — NSE India benchmark index.</t>
         </is>
@@ -33565,7 +34721,7 @@
           <t>Pidilite (y axis)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Yahoo Finance symbol PIDILITIND.NS — Pidilite Industries Ltd, NSE India. Interpreted as the requested 'Pidilite Inc'; there is no separately listed entity by that exact name.</t>
         </is>
@@ -33584,7 +34740,7 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Yahoo Finance chart API (query1.finance.yahoo.com/v8/finance/chart), range=5y, interval=1d, retrieved 2026-09-05.</t>
         </is>
@@ -33596,7 +34752,7 @@
           <t>Period covered</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>2021-09-13 to 2026-09-11 (5 years of daily bars).</t>
         </is>
@@ -33608,7 +34764,7 @@
           <t>Rows on Data sheet</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>1237 trading days common to both series; 1236 daily returns (the first date has no prior close).</t>
         </is>
@@ -33620,7 +34776,7 @@
           <t>Alignment</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Dates are inner-joined, so only sessions on which both the index and the stock traded are kept. This avoids spurious zero or stale returns on non-common holidays.</t>
         </is>
@@ -33632,7 +34788,7 @@
           <t>Prices</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>Both raw Close and Adjusted Close are shown. Adjusted Close is corrected for splits and dividends.</t>
         </is>
@@ -33651,7 +34807,7 @@
           <t>Daily % return</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>(Adjusted Close today / Adjusted Close previous session) - 1, computed on Adjusted Close so the series is a total return. Stored as a fraction and displayed as a percentage.</t>
         </is>
@@ -33663,7 +34819,7 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>Ordinary least squares SLOPE(y, x) with NIFTY 50 returns as x and Pidilite returns as y. This is Pidilite's raw (unadjusted) beta against the NIFTY 50.</t>
         </is>
@@ -33675,7 +34831,7 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Slope is unit-free: it is identical whether both series are expressed as fractions or as percentages.</t>
         </is>
@@ -33687,7 +34843,7 @@
           <t>Annualisation</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Daily volatility x SQRT(252). 252 trading days per year is an assumption, set in cell Regression!B21.</t>
         </is>
@@ -33706,7 +34862,7 @@
           <t>Independent check</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>The workbook's cells hold live formulas, not pasted numbers, and Excel recalculates them on open. The same regression computed independently in Python (numpy least squares) at build time gave: n = 1236  |  slope (beta) = 0.6903  |  intercept = 0.0134% per day  |  R-squared = 0.1973  |  correlation = 0.4442. The Regression sheet's 'Slope cross-check (Cov / Var)' cell is a second, in-sheet check that must match the SLOPE result.</t>
         </is>
@@ -33718,7 +34874,7 @@
           <t>Recalculation</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>This file was written by openpyxl, which stores formulas without cached results. Full-calculation-on-load is set, so Excel or LibreOffice fills in every value the first time the file is opened.</t>
         </is>
@@ -33737,7 +34893,7 @@
           <t>Risk-free rate</t>
         </is>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>6.97% - India 10-year benchmark G-Sec yield as at 10-Sep-2026, Trading Economics (https://tradingeconomics.com/india/government-bond-yield). Cross-checked at 6.96% on 04-Sep-2026. A 10Y sovereign yield is the conventional Rf for an INR-denominated valuation.</t>
         </is>
@@ -33749,7 +34905,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>Linked live to Regression!B4 - the OLS slope computed on this workbook's own daily returns. Not retyped.</t>
         </is>
@@ -33761,7 +34917,7 @@
           <t>Market return</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>^NSEI is a PRICE index and excludes dividends, so a dividend yield of 1.25% (NIFTY 50 long-run average) is added to every price CAGR to reach a total market return.</t>
         </is>
@@ -33773,7 +34929,7 @@
           <t>Why three approaches</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>The trailing 5-year window opens close to the Sep-2021 market peak, so the realised NIFTY 50 total return lands within a few tenths of a percent of the risk-free rate. The resulting risk premium is approximately zero - and on a marginally different start date it goes negative, putting the cost of equity below Rf. Either way it is an artefact of the start date, not an economic result, and cannot be used on its own. Approaches B (10-year realised) and C (forward-looking implied premium) are shown alongside it, and the selected-Ke cell defaults to C.</t>
         </is>
@@ -33785,7 +34941,7 @@
           <t>India ERP</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>7.08% - Damodaran implied India equity risk premium, January 2026 vintage (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), being the mature-market ERP plus a 2.85% India country risk premium at a Baa3 rating. A July-2026 update quotes 7.31%.</t>
         </is>
@@ -33797,7 +34953,7 @@
           <t>10-year CAGRs</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>NIFTY 50 price CAGR 10.49% and Pidilite total-return CAGR 16.46%, both over the 10 years to 11-Sep-2026, computed from the full Yahoo Finance price history (a longer window than this workbook's 5-year Data sheet).</t>
         </is>
@@ -33816,7 +34972,7 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>Pidilite Industries Ltd CONSOLIDATED annual financials, FY2023-FY2026 (years ended 31 March). Retrieved from the Yahoo Finance fundamentals-timeseries API and cross-checked line by line against screener.in (https://www.screener.in/company/PIDILITIND/consolidated/). Both restate the same statements the company files with the exchanges; every figure used agreed between the two sources.</t>
         </is>
@@ -33828,7 +34984,7 @@
           <t>NSE not reachable</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>www.nseindia.com returns HTTP 403 to this environment (NSE blocks datacentre traffic), so the figures could not be pulled from NSE directly. The two sources above carry the same filed consolidated numbers.</t>
         </is>
@@ -33840,7 +34996,7 @@
           <t>Borrowings definition</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>The 'Total borrowings' line is the borrowings figure as reported, which under Ind AS 116 INCLUDES lease liabilities - and finance costs likewise include lease interest, so numerator and denominator are consistent. Pidilite is close to debt-free: of FY2026 borrowings of Rs 417.21 crore, only Rs 105.91 crore is actual borrowing and the rest is lease liability. Dividing total interest by borrowings-excluding-leases would mismatch the two, and is shown on the sheet only as a memo.</t>
         </is>
@@ -33852,7 +35008,7 @@
           <t>Closing vs average</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>The headline follows the requested formula (total interest / total borrowings) on closing balances. A cost of debt on AVERAGE borrowings is shown alongside, since interest accrues across the year.</t>
         </is>
@@ -33871,7 +35027,7 @@
           <t>Weights</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Market value of equity = 1,017,766,288 shares outstanding at 31-Mar-2026 x the latest unadjusted close from the Data sheet. Market value of debt is taken at book: the borrowings are short-dated and largely floating or lease obligations, so book value is a close proxy and is the normal convention.</t>
         </is>
@@ -33883,7 +35039,7 @@
           <t>Shares outstanding</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>1,017,766,288 ordinary shares at 31-Mar-2026 (Yahoo Finance fundamentals; reconciles to the Rs 102 crore equity capital reported by screener.in at Re 1 face value).</t>
         </is>
@@ -33895,7 +35051,7 @@
           <t>Near-zero gearing</t>
         </is>
       </c>
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Debt is under 1% of total capital, so WACC sits within a few basis points of the cost of equity. The sensitivity grid on the WACC sheet shows what the number would become at higher target debt weights, holding the component costs fixed.</t>
         </is>
@@ -33907,38 +35063,117 @@
           <t>Net cash</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Cash and equivalents of Rs 232.49 crore and cash plus short-term investments of Rs 4,215.98 crore at 31-Mar-2026 both exceed total borrowings of Rs 417.21 crore, so Pidilite is net cash. Net debt is negative, which makes a net-debt-weighted WACC meaningless; gross debt is used for the weights.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Free cash flow to firm: FCFF = EBIT x (1 - tax) + D&amp;A - capex - increase in net working capital. Five explicit forecast years (FY2027-FY2031) plus a Gordon-growth terminal value, discounted at the WACC from the WACC sheet. Enterprise value less net debt gives equity value, divided by shares outstanding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>Historical base</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>FY2023-FY2026 consolidated actuals, same Yahoo Finance / screener.in source as the Cost of Debt sheet. EBIT is taken as OPERATING income, which excludes other income - treasury returns are already captured by adding net cash, so counting them in EBIT as well would double count them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>Forecast assumptions</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>Revenue growth fades 10% / 9% / 8% / 7% / 6% toward a 5% terminal rate, against FY2026 actual growth of 11.1% and a three-year CAGR of 7.4%. EBIT margin held flat at the FY2026 level of 21.63% rather than extrapolating the 14.9% to 21.6% climb of the last four years. D&amp;A 2.65% and capex 4.09% of revenue are historical averages; working capital is charged at 6.00% of the INCREASE in revenue. Every one of these is an input cell and can be overwritten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>Valuation date</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>Cash flows are discounted from the 31-Mar-2026 balance sheet date at whole-year end-of-period intervals. No stub adjustment is made for the months already elapsed in FY2027, and no mid-year convention is applied; both would raise the value modestly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>Terminal value</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Carries about 74% of enterprise value, which is normal for a five-year forecast but means the answer is driven mainly by the terminal growth rate and the WACC. The sensitivity grid shows value per share across WACC of 10.85%-12.85% and terminal growth of 4.0%-6.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>The result</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>On these assumptions the DCF values Pidilite far below its market price. That is a statement about the assumptions, not a recommendation. Pidilite trades on a premium multiple (roughly 65x earnings), and a DCF discounting at ~11.9% with 5% perpetual growth cannot reproduce that. The reverse DCF in section 6 shows the market is implying a perpetual growth rate of about 10.5% - above the 6.97% risk-free rate, which no company can sustain forever. The honest reading is that the gap sits in the growth and margin assumptions, and that a five-year fade may simply be too short a runway for this franchise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Raw beta</t>
         </is>
       </c>
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B53" s="41" t="inlineStr">
         <is>
           <t>No Blume or Vasicek adjustment and no risk-free rate is subtracted; this is a total-return beta, not a CAPM excess-return beta.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="B46" s="35" t="inlineStr">
+      <c r="B54" s="41" t="inlineStr">
         <is>
           <t>Beta estimated over a 5-year window is a single point estimate and is not stable over sub-periods.</t>
         </is>

--- a/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
+++ b/analysis/NIFTY50_Pidilite_Daily_Returns_Beta.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Debt" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF 10Y" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$G$1238</definedName>
@@ -4650,7 +4651,7 @@
         <v>1205.65</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>1172.87</v>
+        <v>1172.86</v>
       </c>
       <c r="F156" s="4">
         <f>C156/C155-1</f>
@@ -15025,7 +15026,7 @@
         <v>1357.55</v>
       </c>
       <c r="E571" s="3" t="n">
-        <v>1331.91</v>
+        <v>1331.92</v>
       </c>
       <c r="F571" s="4">
         <f>C571/C570-1</f>
@@ -31691,16 +31692,16 @@
         <v>46276</v>
       </c>
       <c r="B1238" s="3" t="n">
-        <v>23289.55</v>
+        <v>23280.05</v>
       </c>
       <c r="C1238" s="3" t="n">
-        <v>23289.55</v>
+        <v>23280.05</v>
       </c>
       <c r="D1238" s="3" t="n">
-        <v>1555</v>
+        <v>1554.2</v>
       </c>
       <c r="E1238" s="3" t="n">
-        <v>1555</v>
+        <v>1554.2</v>
       </c>
       <c r="F1238" s="4">
         <f>C1238/C1237-1</f>
@@ -34682,7 +34683,1273 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:M67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="100" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>DCF - 10 Year Forecast Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Same business assumptions as the 5-year base case. Only the forecast window and the growth path differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Blue = input   Green = linked from another sheet   Black = formula.  All figures INR crore unless stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1. What this scenario changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Forecast window</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Ten explicit years (FY2027-FY2036) instead of five, then the same terminal value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Growth path</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Fades linearly from 11.0% to 5.6%, roughly 0.6pp a year, landing beside the 5.0% terminal rate. The 5-year case had to cut from 10% to 6% in half the time, which forces the fade through faster than a franchise of this quality plausibly decays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Everything else</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Margin, D&amp;A, capex, working capital intensity, tax, WACC and terminal growth are all unchanged and, where possible, linked directly to the base-case DCF sheet - so any difference in value comes from the runway alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2. Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>EBIT margin, first forecast year</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>FY2026 actual, as in the base case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>EBIT margin, final forecast year</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>Defaults EQUAL to the first year, so margin is held flat and this scenario is a like-for-like test of the runway. Raise it to model operating leverage; the margin is interpolated linearly between the two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>D&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>DCF!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>DCF!B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>NWC % of incremental revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="33">
+        <f>DCF!B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="B16" s="33">
+        <f>DCF!B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>WACC (discount rate)</t>
+        </is>
+      </c>
+      <c r="B17" s="33">
+        <f>DCF!B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f>DCF!B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>3. Free cash flow projection - ten years</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="I21" s="28" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>FY2036E</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Linear fade of about 0.6pp a year from FY2026's actual 11.1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="30">
+        <f>DCF!E7*(1+B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="30">
+        <f>B23*(1+C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="30">
+        <f>C23*(1+D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="30">
+        <f>D23*(1+E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="30">
+        <f>E23*(1+F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="30">
+        <f>F23*(1+G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="30">
+        <f>G23*(1+H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="30">
+        <f>H23*(1+I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="30">
+        <f>I23*(1+J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="30">
+        <f>J23*(1+K22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>FY2027 grows off the FY2026 actual on the DCF sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>EBIT margin</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>$B$11+($B$12-$B$11)*0/9</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>$B$11+($B$12-$B$11)*1/9</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>$B$11+($B$12-$B$11)*2/9</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>$B$11+($B$12-$B$11)*3/9</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>$B$11+($B$12-$B$11)*4/9</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>$B$11+($B$12-$B$11)*5/9</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>$B$11+($B$12-$B$11)*6/9</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>$B$11+($B$12-$B$11)*7/9</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>$B$11+($B$12-$B$11)*8/9</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
+        <f>$B$11+($B$12-$B$11)*9/9</f>
+        <v/>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Linear interpolation between the two margin inputs. Flat by default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B25" s="30">
+        <f>B23*B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="30">
+        <f>C23*C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="30">
+        <f>D23*D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="30">
+        <f>E23*E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="30">
+        <f>F23*F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="30">
+        <f>G23*G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="30">
+        <f>H23*H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="30">
+        <f>I23*I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="30">
+        <f>J23*J24</f>
+        <v/>
+      </c>
+      <c r="K25" s="30">
+        <f>K23*K24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Less: tax on EBIT</t>
+        </is>
+      </c>
+      <c r="B26" s="30">
+        <f>-B25*$B$16</f>
+        <v/>
+      </c>
+      <c r="C26" s="30">
+        <f>-C25*$B$16</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>-D25*$B$16</f>
+        <v/>
+      </c>
+      <c r="E26" s="30">
+        <f>-E25*$B$16</f>
+        <v/>
+      </c>
+      <c r="F26" s="30">
+        <f>-F25*$B$16</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>-G25*$B$16</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>-H25*$B$16</f>
+        <v/>
+      </c>
+      <c r="I26" s="30">
+        <f>-I25*$B$16</f>
+        <v/>
+      </c>
+      <c r="J26" s="30">
+        <f>-J25*$B$16</f>
+        <v/>
+      </c>
+      <c r="K26" s="30">
+        <f>-K25*$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B27" s="30">
+        <f>B25+B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="30">
+        <f>C25+C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="30">
+        <f>D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="30">
+        <f>E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="30">
+        <f>F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="30">
+        <f>G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="30">
+        <f>H25+H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="30">
+        <f>I25+I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="30">
+        <f>J25+J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="30">
+        <f>K25+K26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Add: D&amp;A</t>
+        </is>
+      </c>
+      <c r="B28" s="30">
+        <f>B23*$B$13</f>
+        <v/>
+      </c>
+      <c r="C28" s="30">
+        <f>C23*$B$13</f>
+        <v/>
+      </c>
+      <c r="D28" s="30">
+        <f>D23*$B$13</f>
+        <v/>
+      </c>
+      <c r="E28" s="30">
+        <f>E23*$B$13</f>
+        <v/>
+      </c>
+      <c r="F28" s="30">
+        <f>F23*$B$13</f>
+        <v/>
+      </c>
+      <c r="G28" s="30">
+        <f>G23*$B$13</f>
+        <v/>
+      </c>
+      <c r="H28" s="30">
+        <f>H23*$B$13</f>
+        <v/>
+      </c>
+      <c r="I28" s="30">
+        <f>I23*$B$13</f>
+        <v/>
+      </c>
+      <c r="J28" s="30">
+        <f>J23*$B$13</f>
+        <v/>
+      </c>
+      <c r="K28" s="30">
+        <f>K23*$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Less: capex</t>
+        </is>
+      </c>
+      <c r="B29" s="30">
+        <f>-B23*$B$14</f>
+        <v/>
+      </c>
+      <c r="C29" s="30">
+        <f>-C23*$B$14</f>
+        <v/>
+      </c>
+      <c r="D29" s="30">
+        <f>-D23*$B$14</f>
+        <v/>
+      </c>
+      <c r="E29" s="30">
+        <f>-E23*$B$14</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>-F23*$B$14</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>-G23*$B$14</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>-H23*$B$14</f>
+        <v/>
+      </c>
+      <c r="I29" s="30">
+        <f>-I23*$B$14</f>
+        <v/>
+      </c>
+      <c r="J29" s="30">
+        <f>-J23*$B$14</f>
+        <v/>
+      </c>
+      <c r="K29" s="30">
+        <f>-K23*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Less: increase in NWC</t>
+        </is>
+      </c>
+      <c r="B30" s="30">
+        <f>-(B23-DCF!E7)*$B$15</f>
+        <v/>
+      </c>
+      <c r="C30" s="30">
+        <f>-(C23-B23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="D30" s="30">
+        <f>-(D23-C23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="E30" s="30">
+        <f>-(E23-D23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="F30" s="30">
+        <f>-(F23-E23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="G30" s="30">
+        <f>-(G23-F23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="H30" s="30">
+        <f>-(H23-G23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="I30" s="30">
+        <f>-(I23-H23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="J30" s="30">
+        <f>-(J23-I23)*$B$15</f>
+        <v/>
+      </c>
+      <c r="K30" s="30">
+        <f>-(K23-J23)*$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>FREE CASH FLOW TO FIRM (FCFF)</t>
+        </is>
+      </c>
+      <c r="B31" s="35">
+        <f>B27+B28+B29+B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="35">
+        <f>C27+C28+C29+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="35">
+        <f>D27+D28+D29+D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="35">
+        <f>E27+E28+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="35">
+        <f>F27+F28+F29+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="35">
+        <f>G27+G28+G29+G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="35">
+        <f>H27+H28+H29+H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="35">
+        <f>I27+I28+I29+I30</f>
+        <v/>
+      </c>
+      <c r="J31" s="35">
+        <f>J27+J28+J29+J30</f>
+        <v/>
+      </c>
+      <c r="K31" s="35">
+        <f>K27+K28+K29+K30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="K32" s="36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B33" s="13">
+        <f>1/(1+$B$17)^B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="13">
+        <f>1/(1+$B$17)^C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="13">
+        <f>1/(1+$B$17)^D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="13">
+        <f>1/(1+$B$17)^E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="13">
+        <f>1/(1+$B$17)^F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="13">
+        <f>1/(1+$B$17)^G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="13">
+        <f>1/(1+$B$17)^H32</f>
+        <v/>
+      </c>
+      <c r="I33" s="13">
+        <f>1/(1+$B$17)^I32</f>
+        <v/>
+      </c>
+      <c r="J33" s="13">
+        <f>1/(1+$B$17)^J32</f>
+        <v/>
+      </c>
+      <c r="K33" s="13">
+        <f>1/(1+$B$17)^K32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>PV of FCFF</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>B31*B33</f>
+        <v/>
+      </c>
+      <c r="C34" s="30">
+        <f>C31*C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>D31*D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>E31*E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>F31*F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>G31*G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="30">
+        <f>H31*H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="30">
+        <f>I31*I33</f>
+        <v/>
+      </c>
+      <c r="J34" s="30">
+        <f>J31*J33</f>
+        <v/>
+      </c>
+      <c r="K34" s="30">
+        <f>K31*K33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>4. Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Sum of PV of forecast FCFF</t>
+        </is>
+      </c>
+      <c r="B37" s="30">
+        <f>SUM(B34:K34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value (Gordon growth)</t>
+        </is>
+      </c>
+      <c r="B38" s="30">
+        <f>K31*(1+$B$18)/($B$17-$B$18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B39" s="30">
+        <f>B38*K33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B40" s="30">
+        <f>B37+B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B41" s="16">
+        <f>B39/B40</f>
+        <v/>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Lower than the 5-year case: a longer explicit window shifts weight out of the terminal assumption and into the forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Less: net debt</t>
+        </is>
+      </c>
+      <c r="B42" s="32">
+        <f>DCF!B48</f>
+        <v/>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>Negative - net cash, so this adds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B43" s="30">
+        <f>B40-B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Shares outstanding (crore)</t>
+        </is>
+      </c>
+      <c r="B44" s="37">
+        <f>DCF!B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>INTRINSIC VALUE PER SHARE (INR)</t>
+        </is>
+      </c>
+      <c r="B45" s="38">
+        <f>B43/B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>5. Scenario vs base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>5-year base case, value per share</t>
+        </is>
+      </c>
+      <c r="B48" s="32">
+        <f>DCF!B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>10-year scenario, value per share</t>
+        </is>
+      </c>
+      <c r="B49" s="30">
+        <f>B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Uplift from the longer runway</t>
+        </is>
+      </c>
+      <c r="B50" s="16">
+        <f>B49/B48-1</f>
+        <v/>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>The whole effect of doubling the explicit forecast, with every other assumption held identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Current market price (INR)</t>
+        </is>
+      </c>
+      <c r="B51" s="32">
+        <f>DCF!B52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Upside on base case</t>
+        </is>
+      </c>
+      <c r="B52" s="16">
+        <f>B48/B51-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Upside on this scenario</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>B49/B51-1</f>
+        <v/>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>Still deeply negative. Doubling the runway does not come close to bridging the gap, which is the point of the scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>6. Sensitivity - value per share vs WACC and terminal growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>WACC \ g</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D56" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E56" s="24" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F56" s="24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="B57" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A57)^$B$32:$K$32)+$K$31*(1+B$56)/($A57-B$56)/(1+$A57)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="C57" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A57)^$B$32:$K$32)+$K$31*(1+C$56)/($A57-C$56)/(1+$A57)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="D57" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A57)^$B$32:$K$32)+$K$31*(1+D$56)/($A57-D$56)/(1+$A57)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="E57" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A57)^$B$32:$K$32)+$K$31*(1+E$56)/($A57-E$56)/(1+$A57)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="F57" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A57)^$B$32:$K$32)+$K$31*(1+F$56)/($A57-F$56)/(1+$A57)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="B58" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A58)^$B$32:$K$32)+$K$31*(1+B$56)/($A58-B$56)/(1+$A58)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="C58" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A58)^$B$32:$K$32)+$K$31*(1+C$56)/($A58-C$56)/(1+$A58)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="D58" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A58)^$B$32:$K$32)+$K$31*(1+D$56)/($A58-D$56)/(1+$A58)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="E58" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A58)^$B$32:$K$32)+$K$31*(1+E$56)/($A58-E$56)/(1+$A58)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="F58" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A58)^$B$32:$K$32)+$K$31*(1+F$56)/($A58-F$56)/(1+$A58)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="B59" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A59)^$B$32:$K$32)+$K$31*(1+B$56)/($A59-B$56)/(1+$A59)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="C59" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A59)^$B$32:$K$32)+$K$31*(1+C$56)/($A59-C$56)/(1+$A59)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="D59" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A59)^$B$32:$K$32)+$K$31*(1+D$56)/($A59-D$56)/(1+$A59)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="E59" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A59)^$B$32:$K$32)+$K$31*(1+E$56)/($A59-E$56)/(1+$A59)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="F59" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A59)^$B$32:$K$32)+$K$31*(1+F$56)/($A59-F$56)/(1+$A59)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="B60" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A60)^$B$32:$K$32)+$K$31*(1+B$56)/($A60-B$56)/(1+$A60)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="C60" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A60)^$B$32:$K$32)+$K$31*(1+C$56)/($A60-C$56)/(1+$A60)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="D60" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A60)^$B$32:$K$32)+$K$31*(1+D$56)/($A60-D$56)/(1+$A60)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="E60" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A60)^$B$32:$K$32)+$K$31*(1+E$56)/($A60-E$56)/(1+$A60)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="F60" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A60)^$B$32:$K$32)+$K$31*(1+F$56)/($A60-F$56)/(1+$A60)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="B61" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A61)^$B$32:$K$32)+$K$31*(1+B$56)/($A61-B$56)/(1+$A61)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="C61" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A61)^$B$32:$K$32)+$K$31*(1+C$56)/($A61-C$56)/(1+$A61)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="D61" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A61)^$B$32:$K$32)+$K$31*(1+D$56)/($A61-D$56)/(1+$A61)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="E61" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A61)^$B$32:$K$32)+$K$31*(1+E$56)/($A61-E$56)/(1+$A61)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+      <c r="F61" s="40">
+        <f>(SUMPRODUCT($B$31:$K$31/(1+$A61)^$B$32:$K$32)+$K$31*(1+F$56)/($A61-F$56)/(1+$A61)^$K$32-$B$42)/$B$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Each cell re-runs the full ten-year DCF at that WACC and terminal growth rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>7. Reverse DCF on the ten-year forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Enterprise value at market price</t>
+        </is>
+      </c>
+      <c r="B65" s="32">
+        <f>WACC!B8+WACC!B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value the market implies</t>
+        </is>
+      </c>
+      <c r="B66" s="30">
+        <f>(B65-B37)/K33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Implied perpetual growth rate</t>
+        </is>
+      </c>
+      <c r="B67" s="16">
+        <f>(B66*$B$17-K31)/(B66+K31)</f>
+        <v/>
+      </c>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>Even after ten years of above-terminal growth, the rate needed to justify today's price stays above the 6.97% risk-free rate. That is the useful conclusion: the gap is not an artefact of too short a forecast window.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -34864,7 +36131,7 @@
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>The workbook's cells hold live formulas, not pasted numbers, and Excel recalculates them on open. The same regression computed independently in Python (numpy least squares) at build time gave: n = 1236  |  slope (beta) = 0.6903  |  intercept = 0.0134% per day  |  R-squared = 0.1973  |  correlation = 0.4442. The Regression sheet's 'Slope cross-check (Cov / Var)' cell is a second, in-sheet check that must match the SLOPE result.</t>
+          <t>The workbook's cells hold live formulas, not pasted numbers, and Excel recalculates them on open. The same regression computed independently in Python (numpy least squares) at build time gave: n = 1236  |  slope (beta) = 0.6904  |  intercept = 0.0134% per day  |  R-squared = 0.1973  |  correlation = 0.4442. The Regression sheet's 'Slope cross-check (Cov / Var)' cell is a second, in-sheet check that must match the SLOPE result.</t>
         </is>
       </c>
     </row>
@@ -35148,32 +36415,87 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Caveats</t>
-        </is>
-      </c>
-    </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>Raw beta</t>
-        </is>
-      </c>
-      <c r="B53" s="41" t="inlineStr">
-        <is>
-          <t>No Blume or Vasicek adjustment and no risk-free rate is subtracted; this is a total-return beta, not a CAPM excess-return beta.</t>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>DCF - 10 year scenario</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
         <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>A controlled test, not a second opinion. Margin, D&amp;A, capex, working capital intensity, tax, WACC and terminal growth are all linked straight from the 5-year DCF sheet, so they cannot drift apart. The only differences are the length of the explicit window (ten years, FY2027-FY2036) and the growth path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>Growth path</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
+          <t>Fades linearly by about 0.6pp a year from 11.0% to 5.6%, arriving beside the 5.0% terminal rate. The 5-year case compresses the same journey into half the time, which forces a faster decay than a franchise of this quality plausibly experiences - that compression is exactly what this scenario relaxes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>Margin switch</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>The sheet interpolates EBIT margin linearly between two input cells, both defaulting to the FY2026 level of 21.63%. Left alone the margin is flat, keeping the comparison like for like; raising the final-year cell models operating leverage over the longer horizon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>Value per share rises from about INR 394 to about INR 443, an uplift of roughly 13%, and the terminal value's share of enterprise value falls from about 74% to about 56% - a genuinely better-conditioned model, since less of the answer rests on a single perpetuity assumption. But the valuation gap to the market barely narrows, from about -75% to about -71%, and the reverse DCF still implies a perpetual growth rate above the risk-free rate. The conclusion is that the gap is NOT an artefact of too short a forecast window: it lives in the growth and margin trajectory, or in the risk premium, not in the length of the runway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>Raw beta</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="inlineStr">
+        <is>
+          <t>No Blume or Vasicek adjustment and no risk-free rate is subtracted; this is a total-return beta, not a CAPM excess-return beta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="B54" s="41" t="inlineStr">
+      <c r="B60" s="41" t="inlineStr">
         <is>
           <t>Beta estimated over a 5-year window is a single point estimate and is not stable over sub-periods.</t>
         </is>
